--- a/XBRL-template-MFRS/Group/06-SOCI-NetOfTax.xlsx
+++ b/XBRL-template-MFRS/Group/06-SOCI-NetOfTax.xlsx
@@ -671,10 +671,22 @@
           <t>Other comprehensive income, net of tax, gains (losses) on other items</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="B13" s="21">
+        <f>1*B10+1*B11+1*B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="21">
+        <f>1*C10+1*C11+1*C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>1*D10+1*D11+1*D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>1*E10+1*E11+1*E12</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="12">
       <c r="A14" s="19" t="inlineStr">
@@ -694,19 +706,19 @@
         </is>
       </c>
       <c r="B15" s="24">
-        <f>1*B12+1*B13+1*B14</f>
+        <f>1*B13+1*B14</f>
         <v/>
       </c>
       <c r="C15" s="24">
-        <f>1*C12+1*C13+1*C14</f>
+        <f>1*C13+1*C14</f>
         <v/>
       </c>
       <c r="D15" s="24">
-        <f>1*D12+1*D13+1*D14</f>
+        <f>1*D13+1*D14</f>
         <v/>
       </c>
       <c r="E15" s="24">
-        <f>1*E12+1*E13+1*E14</f>
+        <f>1*E13+1*E14</f>
         <v/>
       </c>
     </row>
@@ -761,19 +773,19 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>1*B18+1*B19</f>
+        <f>1*B18+-1*B19</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>1*C18+1*C19</f>
+        <f>1*C18+-1*C19</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>1*D18+1*D19</f>
+        <f>1*D18+-1*D19</f>
         <v/>
       </c>
       <c r="E20" s="24">
-        <f>1*E18+1*E19</f>
+        <f>1*E18+-1*E19</f>
         <v/>
       </c>
     </row>
@@ -817,19 +829,19 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>1*B22+1*B23</f>
+        <f>1*B22+-1*B23</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>1*C22+1*C23</f>
+        <f>1*C22+-1*C23</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>1*D22+1*D23</f>
+        <f>1*D22+-1*D23</f>
         <v/>
       </c>
       <c r="E24" s="24">
-        <f>1*E22+1*E23</f>
+        <f>1*E22+-1*E23</f>
         <v/>
       </c>
     </row>
@@ -872,10 +884,22 @@
           <t>Other comprehensive income, net of tax, exchange differences on translation of foreign operations</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
+      <c r="B28" s="20">
+        <f>1*B26+-1*B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="20">
+        <f>1*C26+-1*C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="20">
+        <f>1*D26+-1*D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="20">
+        <f>1*E26+-1*E27</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="12">
       <c r="A29" s="17" t="inlineStr">
@@ -928,19 +952,19 @@
         </is>
       </c>
       <c r="B33" s="23">
-        <f>1*B26+1*B27+1*B28+1*B30+1*B31+1*B32</f>
+        <f>1*B30+-1*B31+-1*B32</f>
         <v/>
       </c>
       <c r="C33" s="23">
-        <f>1*C26+1*C27+1*C28+1*C30+1*C31+1*C32</f>
+        <f>1*C30+-1*C31+-1*C32</f>
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>1*D26+1*D27+1*D28+1*D30+1*D31+1*D32</f>
+        <f>1*D30+-1*D31+-1*D32</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>1*E26+1*E27+1*E28+1*E30+1*E31+1*E32</f>
+        <f>1*E30+-1*E31+-1*E32</f>
         <v/>
       </c>
     </row>
@@ -973,19 +997,19 @@
         </is>
       </c>
       <c r="B36" s="23">
-        <f>1*B34+1*B35</f>
+        <f>1*B20+1*B24+1*B28+1*B33+1*B34+1*B35</f>
         <v/>
       </c>
       <c r="C36" s="23">
-        <f>1*C34+1*C35</f>
+        <f>1*C20+1*C24+1*C28+1*C33+1*C34+1*C35</f>
         <v/>
       </c>
       <c r="D36" s="23">
-        <f>1*D34+1*D35</f>
+        <f>1*D20+1*D24+1*D28+1*D33+1*D34+1*D35</f>
         <v/>
       </c>
       <c r="E36" s="23">
-        <f>1*E34+1*E35</f>
+        <f>1*E20+1*E24+1*E28+1*E33+1*E34+1*E35</f>
         <v/>
       </c>
     </row>
@@ -996,19 +1020,19 @@
         </is>
       </c>
       <c r="B37" s="23">
-        <f>1*B11+1*B15+1*B36</f>
+        <f>1*B15+1*B36</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>1*C11+1*C15+1*C36</f>
+        <f>1*C15+1*C36</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>1*D11+1*D15+1*D36</f>
+        <f>1*D15+1*D36</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>1*E11+1*E15+1*E36</f>
+        <f>1*E15+1*E36</f>
         <v/>
       </c>
     </row>
